--- a/ALL/p04-out/Recipes.xlsx
+++ b/ALL/p04-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,26 @@
           <t>Recipe</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Generated At</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Image Ingredients</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,33 +471,139 @@
           <t>Pizza 🍕🍅
 Ingredients:
 - 2 cups all-purpose flour
+- 1 cup warm water
 - 1 packet (2 1/4 tsp) active dry yeast
-- 3/4 cup warm water (110°F)
 - 1 tsp sugar
 - 1 tsp salt
-- 1 tbsp olive oil
-- 1 cup pizza sauce
-- 1 1/2 cups shredded mozzarella cheese
-- Toppings of your choice (pepperoni, bell peppers, mushrooms, etc.)
+- 2 tbsp olive oil
+- 1 cup marinara sauce
+- 2 cups shredded mozzarella cheese
+- 1/2 cup sliced pepperoni
+- Fresh basil leaves for garnish
 Instructions:
-1. In a small bowl, dissolve sugar in warm water and sprinkle yeast on top. Let it sit for about 5 minutes until frothy.
+1. In a small bowl, combine warm water, sugar, and yeast. Let it sit for about 5 minutes until frothy.
 2. In a large mixing bowl, combine flour and salt. Make a well in the center and add the yeast mixture and olive oil.
-3. Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.
+3. Mix until a dough forms. Knead the dough on a floured surface for about 5-7 minutes until smooth.
 4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for about 1 hour or until doubled in size.
-5. Preheat your oven to 475°F (245°C) and prepare a pizza stone or baking sheet.
-6. Roll out the dough on a floured surface to your desired thickness and transfer it to the prepared stone or sheet.
-7. Spread pizza sauce evenly over the crust, leaving a small border around the edges.
-8. Sprinkle shredded mozzarella cheese over the sauce, then add your chosen toppings.
-9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
-10. Remove from the oven and let it cool for a few minutes before slicing.
-11. Serve hot and enjoy your homemade pizza!
+5. Preheat the oven to 475°F (245°C).
+6. Roll out the dough on a floured surface to your desired thickness and transfer it to a pizza stone or baking sheet.
+7. Spread marinara sauce over the dough, leaving a small border around the edges.
+8. Sprinkle shredded mozzarella cheese evenly over the sauce, then top with sliced pepperoni.
+9. Bake in the preheated oven for about 12-15 minutes or until the crust is golden and cheese is bubbly.
+10. Remove from the oven, let it cool slightly, and garnish with fresh basil leaves.
+11. Slice and serve hot.
 Prep Time: 15 minutes
 Cook Time: 15 minutes
 Total Time: 1 hour 30 minutes
 Course: Main Course
 Cuisine: Italian
 Servings: 4
-Calories: ~300 per serving</t>
+Calories: ~350 per serving</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{
+  "name": "pizza",
+  "summary": "This homemade pizza features a crispy crust topped with marinara sauce, mozzarella cheese, and pepperoni. It's a delicious Italian dish perfect for any occasion.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "15",
+  "total_time": "90",
+  "calories": "350",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pizza",
+    "Italian",
+    "cheese",
+    "pepperoni",
+    "homemade",
+    "dough",
+    "baking"
+  ],
+  "notes": "For a crispier crust, bake on a pizza stone. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "warm water"
+    },
+    {
+      "amount": "1",
+      "unit": "packet",
+      "name": "active dry yeast"
+    },
+    {
+      "amount": "1",
+      "unit": "tsp",
+      "name": "sugar"
+    },
+    {
+      "amount": "1",
+      "unit": "tsp",
+      "name": "salt"
+    },
+    {
+      "amount": "2",
+      "unit": "tbsp",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "marinara sauce"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "shredded mozzarella cheese"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "sliced pepperoni"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh basil leaves for garnish"
+    }
+  ],
+  "instructions": [
+    "In a small bowl, combine warm water, sugar, and yeast. Let it sit for about 5 minutes until frothy.",
+    "In a large mixing bowl, combine flour and salt. Make a well in the center and add the yeast mixture and olive oil.",
+    "Mix until a dough forms. Knead the dough on a floured surface for about 5-7 minutes until smooth.",
+    "Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for about 60 minutes or until doubled in size.",
+    "Preheat the oven to 475°F (245°C).",
+    "Roll out the dough on a floured surface to your desired thickness and transfer it to a pizza stone or baking sheet.",
+    "Spread marinara sauce over the dough, leaving a small border around the edges.",
+    "Sprinkle shredded mozzarella cheese evenly over the sauce, then top with sliced pepperoni.",
+    "Bake in the preheated oven for about 12-15 minutes or until the crust is golden and cheese is bubbly.",
+    "Remove from the oven, let it cool slightly, and garnish with fresh basil leaves.",
+    "Slice and serve hot."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a freshly baked pizza topped with melted mozzarella cheese and pepperoni, garnished with fresh basil leaves, served in a clean white ceramic plate on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the pizza center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>flour, water, yeast, sugar, salt, olive oil, marinara sauce, mozzarella cheese, pepperoni, basil leaves, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
     </row>
